--- a/monitor_xlsx/20260121.xlsx
+++ b/monitor_xlsx/20260121.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -75,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -88,6 +91,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,10 +540,6 @@
           <t>-1.05%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -562,10 +562,6 @@
           <t>+1.52%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,10 +584,6 @@
           <t>+0.42%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,10 +606,6 @@
           <t>+3.18%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -640,10 +628,6 @@
           <t>-15.88%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -661,7 +645,6 @@
           <t>-445.68億</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>None億</t>
@@ -699,7 +682,6 @@
           <t>-175.08億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>None億</t>
@@ -710,8 +692,6 @@
           <t>None億</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -729,15 +709,11 @@
           <t>133.33%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,11 +731,6 @@
           <t>-776.37億</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -777,15 +748,11 @@
           <t>22232口</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>None口</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -803,7 +770,6 @@
           <t>29.75億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>None億</t>
@@ -908,10 +874,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1033,7 +995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1068,6 +1030,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1196,7 +1159,6 @@
           <t>0050</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>-84736</v>
       </c>
@@ -1228,7 +1190,6 @@
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>406</v>
       </c>
@@ -1260,7 +1221,6 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>6342</v>
       </c>
@@ -1292,7 +1252,6 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>3300</v>
       </c>
@@ -1324,7 +1283,6 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>-40987</v>
       </c>
@@ -1356,7 +1314,6 @@
           <t>華邦電</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>-7</v>
       </c>
@@ -1388,7 +1345,6 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>341</v>
       </c>
@@ -1420,7 +1376,6 @@
           <t>世芯-KY</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>-953</v>
       </c>
@@ -1452,7 +1407,6 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>-853</v>
       </c>
@@ -1484,7 +1438,6 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>-1154</v>
       </c>
@@ -1516,7 +1469,6 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2502</v>
       </c>
@@ -1548,7 +1500,6 @@
           <t>台新科</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>145</v>
       </c>
@@ -1580,7 +1531,6 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>-6057</v>
       </c>
@@ -1612,7 +1562,6 @@
           <t>昇達科</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>118</v>
       </c>
@@ -1644,7 +1593,6 @@
           <t>耀登</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>-4</v>
       </c>
@@ -1676,15 +1624,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-2.95</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3893</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>830</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2600</v>
+      </c>
       <c r="H19" t="n">
-        <v>-1068</v>
+        <v>-372</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-677</v>
       </c>
       <c r="J19" t="n">
-        <v>-51</v>
+        <v>324</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2462</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12747</v>
       </c>
       <c r="M19" t="n">
-        <v>14462</v>
+        <v>-140152</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1708,7 +1687,6 @@
           <t>波若威</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1045</v>
       </c>
@@ -1726,6 +1704,33 @@
       <c r="W20" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>-514</v>
+      </c>
+      <c r="I21" t="n">
+        <v>148</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2104</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11110</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-47597</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/monitor_xlsx/20260121.xlsx
+++ b/monitor_xlsx/20260121.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,9 @@
     </font>
     <font>
       <color rgb="00008000"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -78,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -92,6 +95,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -995,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1734,6 +1738,59 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>962</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>826</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>18</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260121.xlsx
+++ b/monitor_xlsx/20260121.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1791,6 +1791,59 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>180</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7154</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>242</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1754</v>
+      </c>
+      <c r="H23" t="n">
+        <v>141</v>
+      </c>
+      <c r="I23" t="n">
+        <v>446</v>
+      </c>
+      <c r="J23" t="n">
+        <v>74</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6890</v>
+      </c>
+      <c r="L23" t="n">
+        <v>34593</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-58791</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
